--- a/contoh kontrak.xlsx
+++ b/contoh kontrak.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\File HRD Azza\Dokumen File Azza\File Azza\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\Everiware\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F683D108-89A3-41B4-8EF7-F6ABA066D597}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D316EAE-4BAD-4E76-A078-32C2A406DC3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{67BB30D3-31B7-4D28-92CA-D3002A9CE9D6}"/>
   </bookViews>
@@ -341,22 +341,19 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -366,8 +363,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -387,9 +387,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -427,7 +427,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -533,7 +533,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -675,7 +675,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -693,10 +693,10 @@
     <col min="6" max="6" width="15.7265625" customWidth="1"/>
     <col min="7" max="7" width="24.26953125" customWidth="1"/>
     <col min="8" max="8" width="37.1796875" customWidth="1"/>
-    <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="23.26953125" customWidth="1"/>
-    <col min="11" max="11" width="13" customWidth="1"/>
-    <col min="12" max="12" width="14.6328125" customWidth="1"/>
+    <col min="9" max="9" width="67.54296875" customWidth="1"/>
+    <col min="10" max="10" width="35.36328125" customWidth="1"/>
+    <col min="11" max="11" width="28.36328125" customWidth="1"/>
+    <col min="12" max="12" width="30.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -730,10 +730,10 @@
       <c r="J1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="K1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="18" t="s">
+      <c r="L1" s="11" t="s">
         <v>16</v>
       </c>
       <c r="M1" s="3"/>
@@ -792,171 +792,172 @@
       <c r="I3" s="2"/>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="B10" s="13"/>
-      <c r="C10" s="8" t="s">
+      <c r="B10" s="9"/>
+      <c r="C10" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="B11" s="13"/>
-      <c r="C11" s="8" t="s">
+      <c r="B11" s="9"/>
+      <c r="C11" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
+      <c r="D11" s="17"/>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="B12" s="13"/>
-      <c r="C12" s="8" t="s">
+      <c r="B12" s="9"/>
+      <c r="C12" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="B13" s="13"/>
-      <c r="C13" s="8" t="s">
+      <c r="B13" s="9"/>
+      <c r="C13" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="B14" s="13"/>
-      <c r="C14" s="8" t="s">
+      <c r="B14" s="9"/>
+      <c r="C14" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="B15" s="13"/>
-      <c r="C15" s="8" t="s">
+      <c r="B15" s="9"/>
+      <c r="C15" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="B16" s="13"/>
-      <c r="C16" s="8" t="s">
+      <c r="B16" s="9"/>
+      <c r="C16" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
+      <c r="D16" s="17"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B17" s="13"/>
-      <c r="C17" s="9" t="s">
+      <c r="B17" s="9"/>
+      <c r="C17" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B18" s="13"/>
-      <c r="C18" s="9" t="s">
+      <c r="B18" s="9"/>
+      <c r="C18" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B19" s="13"/>
-      <c r="C19" s="9" t="s">
+      <c r="B19" s="9"/>
+      <c r="C19" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B20" s="14"/>
-      <c r="C20" s="9" t="s">
+      <c r="B20" s="10"/>
+      <c r="C20" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B22" s="16"/>
-      <c r="C22" s="7" t="s">
+      <c r="B22" s="15"/>
+      <c r="C22" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B23" s="16"/>
-      <c r="C23" s="7" t="s">
+      <c r="B23" s="15"/>
+      <c r="C23" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B24" s="17"/>
-      <c r="C24" s="7" t="s">
+      <c r="B24" s="16"/>
+      <c r="C24" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C20:F20"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
-    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="C11:F11"/>
+    <mergeCell ref="C12:F12"/>
     <mergeCell ref="B21:B24"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="C15:F15"/>
@@ -964,12 +965,11 @@
     <mergeCell ref="C17:F17"/>
     <mergeCell ref="C18:F18"/>
     <mergeCell ref="C19:F19"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="C10:F10"/>
-    <mergeCell ref="C11:F11"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="C24:F24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
